--- a/artfynd/A 22412-2026 artfynd.xlsx
+++ b/artfynd/A 22412-2026 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>134403557</v>
       </c>
       <c r="B3" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>134403564</v>
       </c>
       <c r="B4" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>134403519</v>
       </c>
       <c r="B5" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>134403527</v>
       </c>
       <c r="B6" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>134403523</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22412-2026 artfynd.xlsx
+++ b/artfynd/A 22412-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134403557</v>
+        <v>134403537</v>
       </c>
       <c r="B3" t="n">
-        <v>101396</v>
+        <v>8449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,27 +791,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -819,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564029</v>
+        <v>563957</v>
       </c>
       <c r="R3" t="n">
-        <v>6448674</v>
+        <v>6448626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,35 +887,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134403564</v>
+        <v>134403523</v>
       </c>
       <c r="B4" t="n">
-        <v>101396</v>
+        <v>99195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -921,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564106</v>
+        <v>563837</v>
       </c>
       <c r="R4" t="n">
-        <v>6448660</v>
+        <v>6448679</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,35 +993,39 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134403519</v>
+        <v>134403541</v>
       </c>
       <c r="B5" t="n">
-        <v>106317</v>
+        <v>99195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1023,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563825</v>
+        <v>563983</v>
       </c>
       <c r="R5" t="n">
-        <v>6448697</v>
+        <v>6448619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134403527</v>
+        <v>134403519</v>
       </c>
       <c r="B6" t="n">
-        <v>106317</v>
+        <v>106324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563840</v>
+        <v>563825</v>
       </c>
       <c r="R6" t="n">
-        <v>6448675</v>
+        <v>6448697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,39 +1201,35 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134403523</v>
+        <v>134403527</v>
       </c>
       <c r="B7" t="n">
-        <v>99188</v>
+        <v>106324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1231,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563837</v>
+        <v>563840</v>
       </c>
       <c r="R7" t="n">
-        <v>6448679</v>
+        <v>6448675</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1300,414 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134403557</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564029</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6448674</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134403564</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564106</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6448660</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134403516</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563942</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6448848</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134403510</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564153</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6448861</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22412-2026 artfynd.xlsx
+++ b/artfynd/A 22412-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134403537</v>
+        <v>134573661</v>
       </c>
       <c r="B3" t="n">
-        <v>8449</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,43 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St. Solliden, Sm</t>
+          <t>Stora mossen, Stora mossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563957</v>
+        <v>564191</v>
       </c>
       <c r="R3" t="n">
-        <v>6448626</v>
+        <v>6448541</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +845,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,61 +869,61 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134403523</v>
+        <v>134403537</v>
       </c>
       <c r="B4" t="n">
-        <v>99195</v>
+        <v>8449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563837</v>
+        <v>563957</v>
       </c>
       <c r="R4" t="n">
-        <v>6448679</v>
+        <v>6448626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134403541</v>
+        <v>134403523</v>
       </c>
       <c r="B5" t="n">
         <v>99195</v>
@@ -1023,7 +1024,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1036,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563983</v>
+        <v>563837</v>
       </c>
       <c r="R5" t="n">
-        <v>6448619</v>
+        <v>6448679</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,35 +1100,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134403519</v>
+        <v>134403541</v>
       </c>
       <c r="B6" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563825</v>
+        <v>563983</v>
       </c>
       <c r="R6" t="n">
-        <v>6448697</v>
+        <v>6448619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134403527</v>
+        <v>134403519</v>
       </c>
       <c r="B7" t="n">
         <v>106324</v>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563840</v>
+        <v>563825</v>
       </c>
       <c r="R7" t="n">
-        <v>6448675</v>
+        <v>6448697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134403557</v>
+        <v>134403527</v>
       </c>
       <c r="B8" t="n">
-        <v>101403</v>
+        <v>106324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,21 +1319,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564029</v>
+        <v>563840</v>
       </c>
       <c r="R8" t="n">
-        <v>6448674</v>
+        <v>6448675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1410,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134403564</v>
+        <v>134403557</v>
       </c>
       <c r="B9" t="n">
         <v>101403</v>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564106</v>
+        <v>564029</v>
       </c>
       <c r="R9" t="n">
-        <v>6448660</v>
+        <v>6448674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134403516</v>
+        <v>134403564</v>
       </c>
       <c r="B10" t="n">
-        <v>101305</v>
+        <v>101403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563942</v>
+        <v>564106</v>
       </c>
       <c r="R10" t="n">
-        <v>6448848</v>
+        <v>6448660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134403510</v>
+        <v>134403516</v>
       </c>
       <c r="B11" t="n">
-        <v>99001</v>
+        <v>101305</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,16 +1625,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564153</v>
+        <v>563942</v>
       </c>
       <c r="R11" t="n">
-        <v>6448861</v>
+        <v>6448848</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,6 +1713,108 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134403510</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564153</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6448861</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22412-2026 artfynd.xlsx
+++ b/artfynd/A 22412-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403533</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403537</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403523</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403541</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403519</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403527</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403557</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403516</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134573661</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1713,6 +1763,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403564</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,8 +1870,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>